--- a/output/anonymized/anonymized_dataset.xlsx
+++ b/output/anonymized/anonymized_dataset.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -14626,7 +14626,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -14672,7 +14672,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -14718,7 +14718,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -14810,7 +14810,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -15144,7 +15144,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -15194,7 +15194,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -15286,7 +15286,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -15378,7 +15378,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -15424,7 +15424,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -15570,7 +15570,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -21694,7 +21694,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -21790,7 +21790,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -21886,7 +21886,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -21936,7 +21936,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -22028,7 +22028,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -22074,7 +22074,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -22120,7 +22120,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -22166,7 +22166,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -22258,7 +22258,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -22308,7 +22308,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -22354,7 +22354,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -22446,7 +22446,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -22492,7 +22492,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -22538,7 +22538,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -22584,7 +22584,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -22634,7 +22634,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -22680,7 +22680,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -28762,7 +28762,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -28808,7 +28808,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -28858,7 +28858,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -28908,7 +28908,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -28954,7 +28954,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -29000,7 +29000,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -29046,7 +29046,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -29092,7 +29092,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -29138,7 +29138,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -29188,7 +29188,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -29234,7 +29234,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -29330,7 +29330,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -29376,7 +29376,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -29422,7 +29422,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -29468,7 +29468,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -29514,7 +29514,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -29564,7 +29564,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -29610,7 +29610,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -29660,7 +29660,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -29706,7 +29706,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -29752,7 +29752,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>UP FHS</t>
+          <t>Society &amp; Culture</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
